--- a/data/gravel/Brother Big Bro 2025.xlsx
+++ b/data/gravel/Brother Big Bro 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76707F76-62E9-F148-88D9-991E64288951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663C3AC8-178F-8F4B-82EB-E332A08CDAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30060" yWindow="-23680" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -311,9 +311,6 @@
     <t>GBP</t>
   </si>
   <si>
-    <t>https://www.brothercycles.com/shop/frames/big-bro-2025/</t>
-  </si>
-  <si>
     <t>Frame Size</t>
   </si>
   <si>
@@ -342,6 +339,9 @@
   </si>
   <si>
     <t>a8:f31</t>
+  </si>
+  <si>
+    <t>https://www.brothercycles.com/wp-content/uploads/2025/07/L1040772-1200x800.jpg</t>
   </si>
 </sst>
 </file>
@@ -700,7 +700,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -724,7 +724,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -732,7 +732,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -740,19 +740,19 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
         <v>93</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>94</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>95</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>96</v>
-      </c>
-      <c r="F8" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -900,7 +900,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C16">
         <v>445</v>
@@ -1000,7 +1000,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21">
         <v>782</v>
@@ -1242,7 +1242,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Brother Big Bro 2025.xlsx
+++ b/data/gravel/Brother Big Bro 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{663C3AC8-178F-8F4B-82EB-E332A08CDAE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249AB757-7D4D-0F49-B407-5BE9B08105CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30060" yWindow="-23680" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8700" yWindow="520" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>https://www.brothercycles.com/wp-content/uploads/2025/07/L1040772-1200x800.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Kent, United Kingdom</t>
   </si>
 </sst>
 </file>
@@ -681,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1409,6 +1415,14 @@
         <v>91</v>
       </c>
     </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Brother Big Bro 2025.xlsx
+++ b/data/gravel/Brother Big Bro 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249AB757-7D4D-0F49-B407-5BE9B08105CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A192311-75A2-0E4F-AA38-7CEB147E2AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8700" yWindow="520" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,24 @@
   </si>
   <si>
     <t>Kent, United Kingdom</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -687,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1245,181 +1263,211 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>48</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>50</v>
-      </c>
-      <c r="B50">
-        <v>30.9</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>51</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>52</v>
-      </c>
-      <c r="B52">
-        <v>38</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>53</v>
-      </c>
-      <c r="B53">
-        <v>44</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54">
-        <v>180</v>
+        <v>48</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55">
-        <v>180</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B56">
+        <v>30.9</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>58</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>78</v>
+        <v>52</v>
+      </c>
+      <c r="B58">
+        <v>38</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>59</v>
-      </c>
-      <c r="B59" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="B59">
+        <v>44</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B60">
+        <v>180</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>62</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>64</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
+        <v>58</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>65</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>78</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>66</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>67</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>78</v>
+        <v>61</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B68">
-        <v>790.83</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B70">
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>66</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>67</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>68</v>
+      </c>
+      <c r="B74">
+        <v>790.83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>71</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>103</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>104</v>
       </c>
     </row>

--- a/data/gravel/Brother Big Bro 2025.xlsx
+++ b/data/gravel/Brother Big Bro 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A192311-75A2-0E4F-AA38-7CEB147E2AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A2983D2-45B8-5441-9FEE-805690C05246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -338,9 +338,6 @@
     <t>Big Bro</t>
   </si>
   <si>
-    <t>a8:f31</t>
-  </si>
-  <si>
     <t>https://www.brothercycles.com/wp-content/uploads/2025/07/L1040772-1200x800.jpg</t>
   </si>
   <si>
@@ -366,6 +363,18 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>https://www.brothercycles.com/shop/frames/big-bro-2025/</t>
+  </si>
+  <si>
+    <t>a8:f33</t>
   </si>
 </sst>
 </file>
@@ -705,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -748,7 +757,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -756,7 +770,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>101</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -1060,378 +1074,399 @@
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>23</v>
+      <c r="A23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>24</v>
+      <c r="A24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26">
-        <v>2600</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27">
-        <v>700</v>
-      </c>
-      <c r="D27">
-        <v>700</v>
-      </c>
-      <c r="E27" s="1">
-        <v>700</v>
-      </c>
-      <c r="F27">
-        <v>700</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="1">
-        <v>2.25</v>
-      </c>
-      <c r="D28" s="1">
-        <v>2.25</v>
-      </c>
-      <c r="E28" s="1">
-        <v>2.25</v>
-      </c>
-      <c r="F28" s="1">
-        <v>2.25</v>
-      </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="D28">
+        <v>2600</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2.6</v>
+        <v>27</v>
+      </c>
+      <c r="C29">
+        <v>700</v>
+      </c>
+      <c r="D29">
+        <v>700</v>
       </c>
       <c r="E29" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2.6</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
+        <v>700</v>
+      </c>
+      <c r="F29">
+        <v>700</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="E30" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="F30" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>29</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="D31" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="E31" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="F31" s="1">
+        <v>2.6</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40">
-        <v>2.6</v>
+        <v>38</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>40</v>
+      </c>
+      <c r="B42">
+        <v>2.6</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="B43">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="B44">
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>48</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>50</v>
-      </c>
-      <c r="B56">
-        <v>30.9</v>
+        <v>48</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B58">
-        <v>38</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>53</v>
-      </c>
-      <c r="B59">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B60">
-        <v>180</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B61">
-        <v>180</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="B62">
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>90</v>
+        <v>55</v>
+      </c>
+      <c r="B63">
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>59</v>
-      </c>
-      <c r="B65" s="1"/>
+        <v>57</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B67">
-        <v>2</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>62</v>
-      </c>
-      <c r="B68">
-        <v>1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>66</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
+      </c>
+      <c r="B72">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>78</v>
@@ -1439,36 +1474,52 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>68</v>
-      </c>
-      <c r="B74">
-        <v>790.83</v>
+        <v>66</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>69</v>
+        <v>67</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>68</v>
+      </c>
+      <c r="B76">
+        <v>790.83</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>71</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>71</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>102</v>
+      </c>
+      <c r="B80" t="s">
         <v>103</v>
-      </c>
-      <c r="B78" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
